--- a/packages/cts1_mo_tools/src/cts1_mo_tools/cts1_agenda_files/agenda_spreadsheet_template_example.xlsx
+++ b/packages/cts1_mo_tools/src/cts1_mo_tools/cts1_agenda_files/agenda_spreadsheet_template_example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvanq\OneDrive\Documents\GitHub\CTS-SAT-1-Ground-Station\packages\cts1_mo_tools\src\cts1_mo_tools\cts1_agenda_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BDAD0B-6FA9-478C-BF4A-670EBD0840B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6117F1B9-3DA0-4FAD-8F06-18186D2367E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>Start UTC</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>tsexec Start (UTC)</t>
-  </si>
-  <si>
-    <t>Overpass 3</t>
   </si>
   <si>
     <t>tsexec End (UTC)</t>
@@ -184,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -194,21 +191,6 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
@@ -368,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -376,67 +358,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -719,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J19"/>
+  <dimension ref="B1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -736,384 +715,371 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="2:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C2" s="20">
         <v>46320.715277777781</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20">
+        <v>46320.723611111112</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+    </row>
+    <row r="5" spans="2:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="21">
-        <v>46320.723611111112</v>
-      </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="23"/>
-    </row>
-    <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="23"/>
-    </row>
-    <row r="6" spans="2:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="I6" s="10">
+        <v>5</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="s">
+    </row>
+    <row r="7" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0.72430555555555554</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10">
+        <v>5</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0.72442129629629626</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10">
+        <v>5</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0.72453703703703709</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10">
+        <v>5</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0.72465277777777781</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10">
+        <v>5</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0.72476851851851853</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10">
+        <v>5</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="10" t="s">
+      <c r="C12" s="14">
+        <v>0.77847222222222223</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="D13" s="14">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13" t="s">
+      <c r="C14" s="14">
+        <v>3.7534722222222219E-2</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10">
+        <v>1</v>
+      </c>
+      <c r="I14" s="10">
         <v>5</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11">
+      <c r="J14" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="14">
+        <v>3.7881944444444447E-2</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="15">
         <v>1</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I15" s="10">
         <v>5</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="15">
-        <v>0.72430555555555554</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11">
-        <v>5</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="15">
-        <v>0.72442129629629626</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11">
-        <v>1</v>
-      </c>
-      <c r="I9" s="11">
-        <v>5</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="15">
-        <v>0.72453703703703709</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11">
-        <v>1</v>
-      </c>
-      <c r="I10" s="11">
-        <v>5</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="15">
-        <v>0.72465277777777781</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11">
-        <v>5</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="15">
-        <v>0.72476851851851853</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="16">
-        <v>1</v>
-      </c>
-      <c r="I12" s="11">
-        <v>5</v>
-      </c>
-      <c r="J12" s="14" t="s">
+      <c r="J15" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="14">
+        <v>4.0972222222222222E-2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="10" t="s">
+      <c r="F16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="15">
-        <v>0.77847222222222223</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="14" t="s">
+      <c r="C17" s="14">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0.79236111111111107</v>
-      </c>
-      <c r="D14" s="15">
-        <v>3.4722222222222224E-2</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G17" s="11"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="15">
-        <v>3.7534722222222219E-2</v>
-      </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11">
-        <v>1</v>
-      </c>
-      <c r="I15" s="11">
-        <v>5</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="15">
-        <v>3.7881944444444447E-2</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="11">
-        <v>5</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="15">
-        <v>4.0972222222222222E-2</v>
-      </c>
-      <c r="D17" s="15">
-        <v>4.8611111111111112E-2</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="15">
-        <v>5.2083333333333336E-2</v>
-      </c>
-      <c r="D18" s="15">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="18"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="20"/>
+    </row>
+    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C5:J5"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
